--- a/YouTube이슈분석_개인채널_2026-07-28.xlsx
+++ b/YouTube이슈분석_개인채널_2026-07-28.xlsx
@@ -92,10 +92,10 @@
     <t>8:37</t>
   </si>
   <si>
-    <t>본 영상은 실제 동굴 탐사 중 조난되어 608일간 갇혀있던 남자의 생존 실화를 다룬 다큐멘터리입니다. 고립된 환경에서 그가 남긴 성냥갑, 전기 램프, 신발 등 절박했던 생존의 흔적들을 추적하며 동굴 탐사의 위험성과 사고 예방의 중요성을 재구성하여 전달합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 썸네일과 제목을 사용한 스토리텔링 위주의 영상이므로, 정확한 사건의 사실관계 확인을 위해 제공된 공식 자료나 문헌을 함께 찾아보는 것이 좋습니다.</t>
+    <t>이 영상은 동굴 탐사 중 조난당해 608일 동안 갇혀 있었던 남자의 실화를 다룹니다. 성냥갑, 전기 램프, 신발 등 현장에서 발견된 유류품들을 통해 고립된 상황에서의 생존 과정과 마지막 흔적을 추적하며, 사고의 전말과 안전에 대한 경각심을 전달하는 재구성 다큐멘터리입니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 제목과 썸네일로 시청자의 호기심을 유발하는 영상이므로, 실제 사건의 세부 사항은 제공된 공식 자료를 통해 교차 검증하는 것이 좋습니다.</t>
   </si>
   <si>
     <t>▶</t>
@@ -116,106 +116,103 @@
     <t>18:41</t>
   </si>
   <si>
-    <t>이 영상은 1995년 발생한 고베 대지진이 단순한 자연재해를 넘어 아시아 경제와 대한민국 IMF 외환위기에 미친 영향력을 심층 분석합니다. 일본 경제의 핵심이었던 고베 항구의 파괴가 어떻게 글로벌 공급망과 자금 흐름을 뒤흔들고 한국 경제에까지 연쇄적인 충격을 주었는지 사건의 이면을 상세히 다룹니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 제목과 설명이 사건의 경제적 인과관계를 강조하고 있으므로 역사적 사실과 경제적 영향력을 분리해서 이해하는 것이 좋습니다.</t>
-  </si>
-  <si>
-    <t>【일사사】  생방송 중 일본 여성 스트리머를 55차례 공격한 살인범이 동정받는 이유</t>
-  </si>
-  <si>
-    <t>테가미 | 일본 사건사고</t>
+    <t>1995년 발생한 고베 대지진은 일본의 주요 항구 도시를 순식간에 파괴하며 막대한 인명과 재산 피해를 냈습니다. 이 영상은 대지진이 일본 내수 경제를 넘어 아시아 금융 시장에 충격을 주고, 결과적으로 대한민국의 IMF 외환위기 상황까지 직간접적으로 영향을 미쳤던 경제적 연쇄 반응의 과정을 심층 분석합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 제목이 자극적인 클릭베이트 형식을 띠고 있으므로, 경제적 연관성을 역사적 맥락에서 객관적으로 검증하며 시청하는 것을 추천합니다.</t>
+  </si>
+  <si>
+    <t>사건실화 | 존경받던 '군인'에서 '연쇄 살인마'로.. 그가 변한 이유는?</t>
+  </si>
+  <si>
+    <t>유팬더 - 사건실화</t>
+  </si>
+  <si>
+    <t>13:02</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>본 영상은 중국에서 발생한 끔찍한 연쇄 살인 사건인 '항저우 여성 회계사 토막 살인 사건'을 다룹니다. 존경받던 군인 출신이었던 범인이 어떠한 계기로 잔혹한 살인마로 돌변하게 되었는지, 사건의 전말과 그 배경을 언론 보도와 공식 자료를 토대로 상세히 추적하고 분석합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 실제 사건을 바탕으로 한 범죄 실화 콘텐츠이므로 시청 시 정서적 주의가 필요합니다.</t>
+  </si>
+  <si>
+    <t>일본</t>
+  </si>
+  <si>
+    <t>【タカオカ解説】ドイツ“パレード襲撃”事件　容疑者は射殺　イスラム過激派の活動歴があり、当局がすでに監視下に</t>
+  </si>
+  <si>
+    <t>読売テレビニュース</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>4:01</t>
+  </si>
+  <si>
+    <t>독일 베를린 브란덴부르크 문 인근에서 열린 성소수자 권리 행사인 '프라이드 퍼레이드'에서 습격 사건이 발생해 1명이 사망하고 29명이 부상당했습니다. 용의자는 이슬람 과격파 활동 이력으로 당국의 감시를 받던 인물로, 도주 중 경찰에 사살되었습니다. 자유와 인권을 상징하는 역사적 장소에서 발생한 이번 사건은 독일 사회에 큰 충격을 주고 있으며, 테러 동기 등에 대한 조사가 진행 중입니다.</t>
+  </si>
+  <si>
+    <t>⚠️해당 영상은 민감한 테러 사건을 다루고 있으므로, 선정적인 자극보다는 사건의 배경과 독일 사회의 인권적 맥락을 중심으로 이해하는 것이 중요합니다.</t>
+  </si>
+  <si>
+    <t>大阪バイク窃盗未遂　犯人の親が逆ギレ・脅迫するも垢消して逃亡 【ゆっくり解説】</t>
+  </si>
+  <si>
+    <t>ゆっくり事件アーカイブ</t>
+  </si>
+  <si>
+    <t>14:18</t>
+  </si>
+  <si>
+    <t>오사카 신카나오카정에서 발생한 오토바이 절도 미수 사건을 다룹니다. 범인의 부모가 적반하장격으로 피해자를 협박하고 욕설을 퍼부었으나, 비난 여론이 거세지자 소셜 미디어 계정을 삭제하고 도주한 사건의 전말과 온라인상의 파장을 상세히 분석한 영상입니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 본 영상은 자극적인 사건을 선정적으로 다루는 클릭베이트 성향이 있으므로 사실관계 확인 시 주의가 필요합니다.</t>
+  </si>
+  <si>
+    <t>【ゆっくり解説】未だ解明されていない謎の超常現象6選【Part6】</t>
+  </si>
+  <si>
+    <t>闇世界のツーリスト【ゆっくり解説】</t>
+  </si>
+  <si>
+    <t>16:11</t>
+  </si>
+  <si>
+    <t>이 영상은 현대 과학으로도 설명되지 않는 미스터리한 초상 현상 6가지를 다룹니다. 사람을 삼키는 안개, 피오렌티나 UFO 사건, 스스로 움직이는 베츠 미스터리 구체, 배터시 폴터가이스트 현상, 성인의 신부라 불리는 기현상, 그리고 유명한 스킨워커 목장의 괴담까지 흥미로운 사례들을 소개하며 시청자의 호기심을 자극합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 소재를 다루는 미스터리 채널이므로 사실 확인보다는 오락적인 관점에서 시청하는 것이 좋습니다.</t>
+  </si>
+  <si>
+    <t>미국</t>
+  </si>
+  <si>
+    <t>핫이슈</t>
+  </si>
+  <si>
+    <t>Viral TikTok Funny Videos Reaction 😂 | Pashto Comedy Compilation</t>
+  </si>
+  <si>
+    <t>Metal</t>
   </si>
   <si>
     <t>2026-07-25</t>
   </si>
   <si>
-    <t>16:15</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>2025년 도쿄에서 생방송 중이던 여성 스트리머가 시청자에게 55회 공격당해 사망한 사건입니다. 가해자의 범행은 잔혹했으나, 재판 과정에서 두 사람 간의 대여금 갈등과 법적 분쟁 등 범행의 배경이 드러나며 일본 여론이 분열되었습니다. 법원은 범행의 잔인함과 참작 사유를 모두 고려하여 징역 16년을 선고했습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 범죄 사건을 다루는 영상이므로, 사실관계와 여론의 왜곡 가능성을 항상 경계하며 시청하는 태도가 필요합니다.</t>
-  </si>
-  <si>
-    <t>일본</t>
-  </si>
-  <si>
-    <t>【タカオカ解説】ドイツ“パレード襲撃”事件　容疑者は射殺　イスラム過激派の活動歴があり、当局がすでに監視下に</t>
-  </si>
-  <si>
-    <t>読売テレビニュース</t>
-  </si>
-  <si>
-    <t>2026-07-27</t>
-  </si>
-  <si>
-    <t>4:01</t>
-  </si>
-  <si>
-    <t>독일 베를린 브란덴부르크 문 인근에서 열린 '프라이드 퍼레이드' 행사에 무차별 공격이 발생해 사상자가 발생했습니다. 용의자는 당국의 감시 대상이었던 인물로, 도주 과정에서 경찰에 의해 사상했습니다. 자유의 상징인 장소에서 발생한 이번 사건은 독일 사회에 큰 충격을 주었으며, 현재 당국이 정확한 범행 동기를 조사하고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 해당 뉴스는 사건의 자극적인 측면보다 자유와 인권의 상징적 장소에서 발생했다는 사회적 맥락을 중심으로 이해하는 것이 중요합니다.</t>
-  </si>
-  <si>
-    <t>大阪バイク窃盗未遂　犯人の親が逆ギレ・脅迫するも垢消して逃亡 【ゆっくり解説】</t>
-  </si>
-  <si>
-    <t>ゆっくり事件アーカイブ</t>
-  </si>
-  <si>
-    <t>14:18</t>
-  </si>
-  <si>
-    <t>이 영상은 오사카에서 발생한 오토바이 절도 미수 사건을 다룹니다. 절도범의 부모가 범행을 저지른 자녀를 옹호하며 오히려 피해자와 제보자에게 적반하장격인 태도로 협박을 가한 사건을 설명합니다. 이후 이들은 거센 비판과 논란이 일자 SNS 계정을 삭제하고 잠적하며 도주한 사건의 전말을 추적하고 분석합니다.</t>
-  </si>
-  <si>
-    <t>⚠️해당 영상은 자극적인 제목과 썸네일을 활용한 클릭베이트 성격이 강하므로, 실질적인 사실 관계 확인 시 인터넷상의 자극적인 정보에만 의존하지 않도록 주의해야 합니다.</t>
-  </si>
-  <si>
-    <t>미국</t>
-  </si>
-  <si>
-    <t>핫이슈</t>
-  </si>
-  <si>
-    <t>Viral TikTok Funny Videos Reaction 😂 | Pashto Comedy Compilation</t>
-  </si>
-  <si>
-    <t>Metal</t>
-  </si>
-  <si>
     <t>14:48</t>
   </si>
   <si>
-    <t>이 영상은 파슈토어권 틱톡의 인기 유머 영상을 모아 리액션하는 코미디 컴필레이션 콘텐츠입니다. 유튜버 Metal은 짧은 재미있는 클립들을 보여주며 자신의 반응을 담았으며, 시청자들에게 엔터테인먼트를 제공하는 것을 목표로 합니다. 영상은 공정 이용 원칙에 따라 제작되었음을 명시하고 있으며, 게임과 드라마 리뷰 등 다양한 엔터테인먼트 활동을 포함하는 채널의 홍보 성격도 띠고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 클릭베이트 성격이 강한 리액션 영상이므로 실제 내용보다는 가벼운 웃음을 즐기는 용도로 시청하는 것이 좋습니다.</t>
-  </si>
-  <si>
-    <t>Trans Person Goes NUCLEAR on Cops for being Misgendered!</t>
-  </si>
-  <si>
-    <t>Tyrone Magnus</t>
-  </si>
-  <si>
-    <t>2026-07-21</t>
-  </si>
-  <si>
-    <t>15:08</t>
-  </si>
-  <si>
-    <t>플로리다 대학교 캠퍼스 내에서 27세 트랜스젠더 학생 재럿 빅이 자신을 잘못된 성별로 지칭했다는 이유로 경찰에게 격렬하게 항의하며 난동을 부리는 보디캠 영상입니다. 결국 그는 경찰에 의해 수갑이 채워진 채 체포되었으며, 이 영상은 당시의 갈등 상황과 체포 과정을 담고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 해당 영상은 클릭베이트적 요소와 논란이 될 수 있는 주제를 다루고 있으므로, 사실관계 확인 시 보도 자료를 대조하는 비판적 시각이 필요합니다.</t>
+    <t>본 영상은 메탈(Metal) 채널에서 파슈토어권의 바이럴 틱톡 유머 영상들을 시청하며 리액션을 보여주는 편집본입니다. 게임, 드라마 리뷰, 엔터테인먼트 콘텐츠를 다루는 채널의 특성에 맞춰 파슈토어 문화권의 재미있는 짧은 클립들을 모아 코멘터리와 함께 소개하며 시청자들에게 웃음을 전달합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 본 영상은 타인의 창작물을 재사용하여 리액션을 덧붙인 콘텐츠이므로, 자극적인 편집이나 저작권 관련 공정 사용 범위에 유의하며 시청하시기 바랍니다.</t>
   </si>
   <si>
     <t>Why Amazon purchase history may show D4vd's link to teen's murder</t>
@@ -230,25 +227,28 @@
     <t>7:31</t>
   </si>
   <si>
-    <t>가수 D4vd가 14세 소녀 셀레스트 리바스 에르난데스를 살해하고 시신을 훼손한 혐의로 기소되었습니다. 검찰은 아마존 구매 내역을 포함한 결정적인 증거들을 제시하며 사건의 전말을 공개했습니다. NBC4의 에릭 레너드 기자가 2026년 7월 21일 이 충격적인 사건의 재판 상황을 상세히 보도하였습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 유명인의 범죄 사건을 다루는 보도는 자극적인 제목으로 클릭을 유도할 수 있으므로 공식적인 사법 절차와 검증된 보도 내용을 신중하게 확인해야 합니다.</t>
-  </si>
-  <si>
-    <t>Lawlessness In Ireland ! Why Are We Ignoring This??</t>
-  </si>
-  <si>
-    <t>Derek Domino</t>
-  </si>
-  <si>
-    <t>11:16</t>
-  </si>
-  <si>
-    <t>아일랜드 캐번주 버지니아의 러프 레이머 인근에서 발생한 심각한 공공 질서 문란 및 폭력 사태를 다룹니다. 미성년자 5명이 체포되었으며 부상자가 발생했습니다. 영상은 흉기 사용 의혹 등 사건의 전말과 미확인 정보들을 검증하며 아일랜드 내 치안 부재 문제를 비판적으로 분석합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 본 영상은 자극적인 제목과 함께 사건의 세부 사항을 다루고 있으므로, 사실 확인을 위해 아일랜드 공영 방송이나 가르다(Garda) 공식 발표와 같은 신뢰할 수 있는 매체의 뉴스를 병행하여 확인하는 것이 좋습니다.</t>
+    <t>가수 D4vd가 14세 소녀 셀레스트 리바스 에르난데스를 살해하고 시신을 훼손한 혐의로 기소되었습니다. 검찰은 아마존 구매 내역을 포함한 결정적인 증거를 바탕으로 범행 연관성을 입증하고 있으며, 본 리포트는 해당 사건의 수사 과정과 법정 제출 증거를 상세히 다루고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 유명 인사의 범죄 연루 의혹을 다루는 보도는 자극적인 제목과 클릭베이트 형식을 띨 수 있으므로 공식적인 사법 절차와 수사 결과를 위주로 확인하는 것이 좋습니다.</t>
+  </si>
+  <si>
+    <t>Nolan Wells Death: Police Are Looking at the WRONG BOAT</t>
+  </si>
+  <si>
+    <t>Willie D Live</t>
+  </si>
+  <si>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>13:54</t>
+  </si>
+  <si>
+    <t>윌리 D는 놀란 웰스 사망 사건에 대해 당국이 은폐를 시도하고 있다고 주장하며 비판합니다. 특히 변호사 잭 팔미에리가 제기한 '두 척의 보트' 이론을 반박하며, 사건의 진실을 규명하기 위해 증거를 면밀히 분석하고 의문을 제기하는 트루 크라임 분석 영상입니다.</t>
+  </si>
+  <si>
+    <t>⚠️본 영상은 자극적인 추측과陰모론적 성향을 띠고 있으므로, 실제 사법 당국의 공식 발표와 객관적인 수사 기록을 교차 검증하는 태도가 필요합니다.</t>
   </si>
   <si>
     <t>William TAKES ACTION! Camilla's Son THROWN OUT After SHOCKINGLY IMMORAL Behavior At Windsor!</t>
@@ -260,88 +260,88 @@
     <t>18:30</t>
   </si>
   <si>
-    <t>이 영상은 윈저성에서 발생했다고 주장되는 카밀라 왕비의 아들 톰 파커 볼스와 관련된 논란을 다룹니다. 특히 윌리엄 왕세자의 개입 여부와 궁중 의전 문제, 왕실 내부의 긴장 관계에 대한 추측성 보도들을 종합적으로 분석하며 왕실의 전통과 현대적 상황 속에서의 대중적 관심을 고찰합니다.</t>
-  </si>
-  <si>
-    <t>⚠️해당 영상은 제목에서 강력한 갈등을 암시하고 있으나, 신뢰할 수 있는 공식 출처가 부족한 클릭베이트 형태의 주장이므로 내용 확인 시 주의가 필요합니다.</t>
+    <t>본 영상은 윈저성에서 발생한 카밀라 왕비 아들의 부적절한 행동 논란과 그에 따른 윌리엄 왕자의 대응을 다루고 있습니다. 왕실 내부의 규율 문제와 왕실 가족 간의 긴장 관계에 대한 대중의 의혹과 다양한 매체의 보도 내용을 분석하며, 왕실의 전통과 역사적 배경 속에서 이번 사건이 가지는 의미를 살펴봅니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 본 영상은 자극적인 제목과 썸네일을 사용하는 전형적인 클릭베이트 콘텐츠이므로, 공식적인 왕실 발표가 없는 한 신뢰할 수 있는 언론 매체의 검증된 보도를 확인하는 것이 좋습니다.</t>
   </si>
   <si>
     <t>라이징스타</t>
   </si>
   <si>
-    <t>【大谷翔平】「大谷にぶつける」と豪語した韓国人投手が前代未聞の不正退場！「山本や大谷と同列」と擁護する韓国メディアをレジェンド一同が完全論破！【海外の反応 MLBメジャー 野球】</t>
-  </si>
-  <si>
-    <t>大谷メジャーインサイトJP</t>
-  </si>
-  <si>
-    <t>22:24</t>
-  </si>
-  <si>
-    <t>본 영상은 오타니 쇼헤이를 위협하겠다고 발언한 한국 투수가 부정 투구로 퇴장당한 사건을 다룹니다. 해당 선수를 오타니나 야마모토와 동급으로 치켜세우는 한국 언론의 보도에 대해, 메이저리그 전설들과 해외 전문가들이 이를 비판하고 논리적으로 반박하는 반응을 중점적으로 분석합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 썸네일과 제목을 사용한 채널이므로, 팩트 체크를 위해 공식적인 MLB 경기 기록 및 공신력 있는 언론사의 보도를 함께 확인하는 것이 좋습니다.</t>
-  </si>
-  <si>
-    <t>Jungkook's Funniest Moment at Stray Kids' Concert Went Unexpectedly Viral</t>
-  </si>
-  <si>
-    <t>KookFeed</t>
-  </si>
-  <si>
-    <t>5:03</t>
-  </si>
-  <si>
-    <t>본 영상은 스트레이 키즈 콘서트에서 포착된 방탄소년단 정국의 인간미 넘치는 순간을 다룹니다. 특히 펠릭스의 선글라스를 착용한 에피소드부터 방찬에게 손을 흔드는 모습, 관객석에서 즐겁게 춤추는 정국의 천진난만한 태도를 분석하며, 대중들이 왜 이 순간에 열광했는지 그 이유를 상세히 조명합니다.</t>
-  </si>
-  <si>
-    <t>⚠️해당 영상은 제목에서 강력한 호기심을 유발하고 있으나, 실제 내용은 팬 커뮤니티에서 화제가 된 짧은 클립들을 나열한 편집 영상에 가깝습니다.</t>
-  </si>
-  <si>
-    <t>【大谷翔平】山本由伸の日米通算100勝を祝福...フリーマンが明かした大谷翔平の極秘サプライズ夕食会に世間が騒然【海外の反応・MLB】</t>
-  </si>
-  <si>
-    <t>大谷感動物語</t>
-  </si>
-  <si>
-    <t>26:09</t>
-  </si>
-  <si>
-    <t>야구 선수 야마모토 요시노부의 미일 통산 100승 달성을 축하하기 위해 오타니 쇼헤이가 동료들과 함께 극비 서프라이즈 저녁 식사 자리를 마련했습니다. 프레디 프리먼을 통해 밝혀진 오타니의 세심한 배려와 두 사람의 깊은 신뢰 관계는 팬들과 언론에 큰 감동을 주며 화제가 되고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 썸네일과 제목으로 조회수를 유도하는 채널이므로 정보의 출처와 사실 여부를 확인하며 시청하는 것이 좋습니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BTS #viral </t>
-  </si>
-  <si>
-    <t>Favour Nolly</t>
-  </si>
-  <si>
-    <t>6:13</t>
-  </si>
-  <si>
-    <t>본 영상은 BTS의 무대 영상이나 활동 모습을 편집한 짧은 클립으로 보입니다. 특정 대사나 자막 없이 BTS의 역동적인 퍼포먼스나 멤버들의 매력을 강조하는 숏폼 형식의 콘텐츠이며, 조회수 유도를 목적으로 하는 바이럴 홍보 영상의 전형적인 구성을 띠고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 클릭베이트 성격이 강한 채널의 영상이므로 시청 전 자극적인 제목이나 썸네일에 주의가 필요합니다.</t>
-  </si>
-  <si>
-    <t>Fareed Zakaria GPS 7/26/26 | CNN Breaking News Today July 26, 2026</t>
-  </si>
-  <si>
-    <t>Kite update</t>
-  </si>
-  <si>
-    <t>31:29</t>
-  </si>
-  <si>
-    <t>이 영상은 CNN의 시사 프로그램 'Fareed Zakaria GPS' 2026년 7월 26일 자 에피소드입니다. 파리드 자카리아가 세계 지도자, 전문가들과 함께 최신 국제 정치 이슈를 심층 분석하고 독점 보도와 전문가 논평을 통해 글로벌 현안을 다각도로 조명합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 실제 방송 내용보다 조회수를 목적으로 편집된 짜깁기 영상일 가능성이 높으니 신뢰성 있는 출처인지 재확인하세요.</t>
+    <t>BANGLADESH🇧🇩CC TV FOOTAGE VIRAL VIDEO 2026🇧🇩EP 19🇧🇩MONSOON</t>
+  </si>
+  <si>
+    <t>MONSOON</t>
+  </si>
+  <si>
+    <t>4:46</t>
+  </si>
+  <si>
+    <t>이 영상은 '방글라데시 CCTV 영상'이라는 제목을 내세우고 있으나, 구체적인 사건 현장이나 범죄 상황을 담은 실제 CCTV 자료는 포함되어 있지 않습니다. 단순히 자극적인 제목과 썸네일을 활용하여 조회수를 유도하는 클릭베이트 형식의 콘텐츠로, 실제 영상 내용과는 연관성이 매우 낮습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 제목이나 CCTV 영상임을 강조하며 호기심을 유도하는 영상은 대부분 실제 정보가 없는 클릭베이트일 가능성이 높으므로 주의가 필요합니다.</t>
+  </si>
+  <si>
+    <t>28 July  |  Aaj Ki 25 Sabse Badi Khabrein  |  Top 25 Breaking news Today  |  Ravish Kumar Prime Time</t>
+  </si>
+  <si>
+    <t>MS News 72</t>
+  </si>
+  <si>
+    <t>7:32</t>
+  </si>
+  <si>
+    <t>해당 영상은 7월 28일 인도의 정치, 경제, 스포츠 등 주요 분야의 25가지 핵심 뉴스를 다루는 '프라임 타임' 뉴스 요약본입니다. 라비쉬 쿠마르의 진행을 통해 인도는 물론 전 세계의 급박한 현안을 신속하고 정확하게 전달하며, 시청자들에게 당일의 주요 이슈를 빠르게 파악할 수 있는 정보를 제공합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 제목에 특정 날짜와 함께 '가장 큰 뉴스'를 강조하는 전형적인 클릭베이트 형식을 띠고 있어, 실제 정보의 깊이보다 단순 뉴스 나열일 가능성이 높으니 비판적으로 시청하세요.</t>
+  </si>
+  <si>
+    <t>Double Occupancy Full Movie 🎥🍿 || #South #Movie #best_movie #trendingshorts #trendingvideo #viral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PUNEET PAL </t>
+  </si>
+  <si>
+    <t>2:10:44</t>
+  </si>
+  <si>
+    <t>본 영상은 유튜브 채널 PUNEET PAL에 게시된 'Double Occupancy'라는 제목의 풀버전 영화입니다. 구체적인 줄거리 정보가 제공되지 않으며, 제목을 통해 일반적인 남부 인도 영화 스타일의 장르물을 다루고 있음을 유추할 수 있습니다. 짧은 시간 내에 콘텐츠 소비를 유도하는 전형적인 영화 홍보형 업로드 방식입니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 제목과 해시태그를 통해 클릭을 유도하는 콘텐츠이므로, 시청 전 실제 영화의 정식 개봉 여부와 저작권 출처를 확인하는 것이 좋습니다.</t>
+  </si>
+  <si>
+    <t>ယနေ့ ဇူလိုင်လ ၂၈ ရက် မြန်မာနှင့် ကမ္ဘာ့သတင်းများ | Burmese News Radio | July 28, 2026 #မြန်မာသတင်း</t>
+  </si>
+  <si>
+    <t>Burmese News Radio</t>
+  </si>
+  <si>
+    <t>30:04</t>
+  </si>
+  <si>
+    <t>2026년 7월 28일 미얀마 주요 뉴스입니다. 국내 물가 상승으로 계란과 양파 가격이 사상 최고치를 기록했으며, 해외 체류 미얀마 노동자들에게 군사정권이 강제로 외화 송금을 압박하고 있습니다. 또한 미야와디 지역에서 군사정권 부대의 피해와 투항 소식 등 긴박한 군사 상황을 상세히 보도합니다.</t>
+  </si>
+  <si>
+    <t>미얀마의 경제난과 군사적 긴장 상황이 날로 심화되고 있음을 확인할 수 있는 뉴스입니다.</t>
+  </si>
+  <si>
+    <t>Hackers Just Ruined A Billion Dollar Music Industry</t>
+  </si>
+  <si>
+    <t>Daniel Thirtle</t>
+  </si>
+  <si>
+    <t>5:28</t>
+  </si>
+  <si>
+    <t>유명 래퍼들의 미공개 음원과 콘텐츠가 대규모로 유출되어 온라인에서 큰 화제가 된 사건을 다룹니다. 드레이크, 켄드릭 라마, 플레이보이 카티 등 정상급 아티스트들의 데이터가 해킹을 통해 소셜 미디어와 음원 플랫폼으로 유포된 정황을 분석하며, 이러한 정보 보안 위협이 음악 산업에 미치는 파급력을 조명합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 소재로 호기심을 유도하는 클릭베이트성 영상일 수 있으니, 정보의 출처와 사실 여부를 비판적으로 검토하는 것이 중요합니다.</t>
   </si>
 </sst>
 </file>
@@ -813,22 +813,22 @@
         <v>24</v>
       </c>
       <c r="I2" s="3">
-        <v>179046</v>
+        <v>196092</v>
       </c>
       <c r="J2" s="3">
-        <v>2741</v>
+        <v>2880</v>
       </c>
       <c r="K2" s="3">
-        <v>351</v>
+        <v>367</v>
       </c>
       <c r="L2" s="3">
-        <v>29003</v>
+        <v>27695</v>
       </c>
       <c r="M2" s="3">
         <v>176000</v>
       </c>
       <c r="N2" s="4">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="O2" s="5" t="s">
         <v>25</v>
@@ -869,22 +869,22 @@
         <v>32</v>
       </c>
       <c r="I3" s="3">
-        <v>141538</v>
+        <v>165470</v>
       </c>
       <c r="J3" s="3">
-        <v>2897</v>
+        <v>3203</v>
       </c>
       <c r="K3" s="3">
-        <v>357</v>
+        <v>398</v>
       </c>
       <c r="L3" s="3">
-        <v>35452</v>
+        <v>32675</v>
       </c>
       <c r="M3" s="3">
         <v>1130000</v>
       </c>
       <c r="N3" s="4">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="O3" s="5" t="s">
         <v>33</v>
@@ -919,34 +919,34 @@
         <v>36</v>
       </c>
       <c r="G4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="3">
+        <v>41034</v>
+      </c>
+      <c r="J4" s="3">
+        <v>376</v>
+      </c>
+      <c r="K4" s="3">
+        <v>16</v>
+      </c>
+      <c r="L4" s="3">
+        <v>4815</v>
+      </c>
+      <c r="M4" s="3">
+        <v>9750</v>
+      </c>
+      <c r="N4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I4" s="3">
-        <v>72801</v>
-      </c>
-      <c r="J4" s="3">
-        <v>593</v>
-      </c>
-      <c r="K4" s="3">
-        <v>310</v>
-      </c>
-      <c r="L4" s="3">
-        <v>14808</v>
-      </c>
-      <c r="M4" s="3">
-        <v>10000</v>
-      </c>
-      <c r="N4" s="2" t="s">
+      <c r="O4" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="P4" s="5" t="s">
         <v>40</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>41</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>27</v>
@@ -960,7 +960,7 @@
         <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>20</v>
@@ -969,40 +969,40 @@
         <v>1</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="I5" s="3">
-        <v>35582</v>
+        <v>48785</v>
       </c>
       <c r="J5" s="3">
-        <v>345</v>
+        <v>511</v>
       </c>
       <c r="K5" s="3">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="L5" s="3">
-        <v>13345</v>
+        <v>11335</v>
       </c>
       <c r="M5" s="3">
         <v>986000</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="P5" s="5" t="s">
         <v>47</v>
-      </c>
-      <c r="P5" s="5" t="s">
-        <v>48</v>
       </c>
       <c r="Q5" s="2" t="s">
         <v>27</v>
@@ -1016,7 +1016,7 @@
         <v>18</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>20</v>
@@ -1025,40 +1025,40 @@
         <v>2</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I6" s="3">
-        <v>44113</v>
+        <v>47185</v>
       </c>
       <c r="J6" s="3">
-        <v>1257</v>
+        <v>1337</v>
       </c>
       <c r="K6" s="3">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="L6" s="3">
-        <v>11163</v>
+        <v>10480</v>
       </c>
       <c r="M6" s="3">
         <v>10500</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O6" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="P6" s="5" t="s">
         <v>52</v>
-      </c>
-      <c r="P6" s="5" t="s">
-        <v>53</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>27</v>
@@ -1072,49 +1072,49 @@
         <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="2">
+        <v>3</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="G7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D7" s="2">
-        <v>1</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="I7" s="3">
+        <v>27052</v>
+      </c>
+      <c r="J7" s="3">
+        <v>827</v>
+      </c>
+      <c r="K7" s="3">
+        <v>30</v>
+      </c>
+      <c r="L7" s="3">
+        <v>7772</v>
+      </c>
+      <c r="M7" s="3">
+        <v>796000</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O7" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="P7" s="5" t="s">
         <v>57</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I7" s="3">
-        <v>56440</v>
-      </c>
-      <c r="J7" s="3">
-        <v>3820</v>
-      </c>
-      <c r="K7" s="3">
-        <v>385</v>
-      </c>
-      <c r="L7" s="3">
-        <v>21671</v>
-      </c>
-      <c r="M7" s="3">
-        <v>148000</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="O7" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="P7" s="5" t="s">
-        <v>60</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>27</v>
@@ -1128,49 +1128,49 @@
         <v>18</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D8" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="3">
+        <v>66691</v>
+      </c>
+      <c r="J8" s="3">
+        <v>4238</v>
+      </c>
+      <c r="K8" s="3">
+        <v>408</v>
+      </c>
+      <c r="L8" s="3">
+        <v>20677</v>
+      </c>
+      <c r="M8" s="3">
+        <v>149000</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O8" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="I8" s="3">
-        <v>44993</v>
-      </c>
-      <c r="J8" s="3">
-        <v>2834</v>
-      </c>
-      <c r="K8" s="3">
-        <v>533</v>
-      </c>
-      <c r="L8" s="3">
-        <v>12869</v>
-      </c>
-      <c r="M8" s="3">
-        <v>2040000</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="O8" s="5" t="s">
+      <c r="P8" s="5" t="s">
         <v>65</v>
-      </c>
-      <c r="P8" s="5" t="s">
-        <v>66</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>27</v>
@@ -1184,7 +1184,7 @@
         <v>18</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>20</v>
@@ -1193,40 +1193,40 @@
         <v>1</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="I9" s="3">
-        <v>127320</v>
+        <v>127835</v>
       </c>
       <c r="J9" s="3">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="K9" s="3">
         <v>322</v>
       </c>
       <c r="L9" s="3">
-        <v>14572</v>
+        <v>13523</v>
       </c>
       <c r="M9" s="3">
-        <v>407000</v>
+        <v>408000</v>
       </c>
       <c r="N9" s="4">
         <v>0.31</v>
       </c>
       <c r="O9" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="P9" s="5" t="s">
         <v>71</v>
-      </c>
-      <c r="P9" s="5" t="s">
-        <v>72</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>27</v>
@@ -1240,7 +1240,7 @@
         <v>18</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>20</v>
@@ -1249,34 +1249,34 @@
         <v>2</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>75</v>
       </c>
       <c r="I10" s="3">
-        <v>24533</v>
+        <v>55997</v>
       </c>
       <c r="J10" s="3">
-        <v>2235</v>
+        <v>2994</v>
       </c>
       <c r="K10" s="3">
-        <v>690</v>
+        <v>951</v>
       </c>
       <c r="L10" s="3">
-        <v>11970</v>
+        <v>18726</v>
       </c>
       <c r="M10" s="3">
-        <v>94200</v>
+        <v>1170000</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O10" s="5" t="s">
         <v>76</v>
@@ -1296,7 +1296,7 @@
         <v>18</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>20</v>
@@ -1317,22 +1317,22 @@
         <v>80</v>
       </c>
       <c r="I11" s="3">
-        <v>35781</v>
+        <v>54920</v>
       </c>
       <c r="J11" s="3">
-        <v>743</v>
+        <v>1119</v>
       </c>
       <c r="K11" s="3">
-        <v>120</v>
+        <v>184</v>
       </c>
       <c r="L11" s="3">
-        <v>9755</v>
+        <v>11855</v>
       </c>
       <c r="M11" s="3">
-        <v>24500</v>
+        <v>26300</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O11" s="5" t="s">
         <v>81</v>
@@ -1430,7 +1430,7 @@
         <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>83</v>
@@ -1445,28 +1445,28 @@
         <v>85</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>86</v>
       </c>
       <c r="I2" s="3">
-        <v>198274</v>
+        <v>91114</v>
       </c>
       <c r="J2" s="3">
-        <v>1446</v>
+        <v>595</v>
       </c>
       <c r="K2" s="3">
-        <v>451</v>
+        <v>7</v>
       </c>
       <c r="L2" s="3">
         <v>0</v>
       </c>
       <c r="M2" s="3">
-        <v>141</v>
+        <v>652</v>
       </c>
       <c r="N2" s="4">
-        <v>1406</v>
+        <v>140</v>
       </c>
       <c r="O2" s="5" t="s">
         <v>87</v>
@@ -1486,7 +1486,7 @@
         <v>18</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>83</v>
@@ -1501,28 +1501,28 @@
         <v>90</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>91</v>
       </c>
       <c r="I3" s="3">
-        <v>126612</v>
+        <v>187018</v>
       </c>
       <c r="J3" s="3">
-        <v>5449</v>
+        <v>2341</v>
       </c>
       <c r="K3" s="3">
-        <v>151</v>
+        <v>105</v>
       </c>
       <c r="L3" s="3">
         <v>0</v>
       </c>
       <c r="M3" s="3">
-        <v>284</v>
+        <v>1470</v>
       </c>
       <c r="N3" s="4">
-        <v>446</v>
+        <v>127</v>
       </c>
       <c r="O3" s="5" t="s">
         <v>92</v>
@@ -1542,7 +1542,7 @@
         <v>18</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>83</v>
@@ -1557,28 +1557,28 @@
         <v>95</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>96</v>
       </c>
       <c r="I4" s="3">
-        <v>126900</v>
+        <v>161384</v>
       </c>
       <c r="J4" s="3">
-        <v>1426</v>
+        <v>3921</v>
       </c>
       <c r="K4" s="3">
-        <v>36</v>
+        <v>105</v>
       </c>
       <c r="L4" s="3">
         <v>0</v>
       </c>
       <c r="M4" s="3">
-        <v>553</v>
+        <v>2390</v>
       </c>
       <c r="N4" s="4">
-        <v>229</v>
+        <v>68</v>
       </c>
       <c r="O4" s="5" t="s">
         <v>97</v>
@@ -1598,7 +1598,7 @@
         <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>83</v>
@@ -1613,28 +1613,28 @@
         <v>100</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>101</v>
       </c>
       <c r="I5" s="3">
-        <v>132267</v>
+        <v>279500</v>
       </c>
       <c r="J5" s="3">
-        <v>332</v>
+        <v>4891</v>
       </c>
       <c r="K5" s="3">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="L5" s="3">
         <v>0</v>
       </c>
       <c r="M5" s="3">
-        <v>873</v>
+        <v>9110</v>
       </c>
       <c r="N5" s="4">
-        <v>152</v>
+        <v>31</v>
       </c>
       <c r="O5" s="5" t="s">
         <v>102</v>
@@ -1654,7 +1654,7 @@
         <v>18</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>83</v>
@@ -1669,28 +1669,28 @@
         <v>105</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>106</v>
       </c>
       <c r="I6" s="3">
-        <v>321351</v>
+        <v>69999</v>
       </c>
       <c r="J6" s="3">
-        <v>3877</v>
+        <v>3417</v>
       </c>
       <c r="K6" s="3">
-        <v>301</v>
+        <v>354</v>
       </c>
       <c r="L6" s="3">
         <v>0</v>
       </c>
       <c r="M6" s="3">
-        <v>3420</v>
+        <v>2580</v>
       </c>
       <c r="N6" s="4">
-        <v>94</v>
+        <v>27</v>
       </c>
       <c r="O6" s="5" t="s">
         <v>107</v>
